--- a/payment_forms/023_handmade_bag_order_form_worldpay_uk_payment_form--payment_forms.xlsx
+++ b/payment_forms/023_handmade_bag_order_form_worldpay_uk_payment_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'worldpay_uk'}</t>
+          <t>worldpay_uk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Worldpay UK'}</t>
+          <t>Worldpay UK</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'apple_pay'}</t>
+          <t>apple_pay</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Apple Pay'}</t>
+          <t>Apple Pay</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'google_pay'}</t>
+          <t>google_pay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Google Pay'}</t>
+          <t>Google Pay</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'amazon_pay'}</t>
+          <t>amazon_pay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Amazon Pay'}</t>
+          <t>Amazon Pay</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'facebook_pay'}</t>
+          <t>facebook_pay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Facebook Pay'}</t>
+          <t>Facebook Pay</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Bank transfer'}</t>
+          <t>Bank transfer</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'cheque'}</t>
+          <t>cheque</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Cheque'}</t>
+          <t>Cheque</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'mobile_wallet'}</t>
+          <t>mobile_wallet</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Mobile wallet'}</t>
+          <t>Mobile wallet</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'cryptocurrency'}</t>
+          <t>cryptocurrency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Cryptocurrency'}</t>
+          <t>Cryptocurrency</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'handmade'}</t>
+          <t>handmade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Handmade'}</t>
+          <t>Handmade</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'handmade_and_printed'}</t>
+          <t>handmade_and_printed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Handmade and printed'}</t>
+          <t>Handmade and printed</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'handmade_and_custom'}</t>
+          <t>handmade_and_custom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Handmade and custom'}</t>
+          <t>Handmade and custom</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'wholesale'}</t>
+          <t>wholesale</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Wholesale'}</t>
+          <t>Wholesale</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'gbp'}</t>
+          <t>gbp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'GBP'}</t>
+          <t>GBP</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'cad'}</t>
+          <t>cad</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'CAD'}</t>
+          <t>CAD</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'aud'}</t>
+          <t>aud</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'AUD'}</t>
+          <t>AUD</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'cny'}</t>
+          <t>cny</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'CNY'}</t>
+          <t>CNY</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'inr'}</t>
+          <t>inr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'INR'}</t>
+          <t>INR</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'jpy'}</t>
+          <t>jpy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'JPY'}</t>
+          <t>JPY</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'cny'}</t>
+          <t>krw</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'CNY'}</t>
+          <t>KRW</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'krw'}</t>
+          <t>twd</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'KRW'}</t>
+          <t>TWD</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'twd'}</t>
+          <t>mxn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'TWD'}</t>
+          <t>MXN</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_'mxn'}</t>
+          <t>cop</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': 'MXN'}</t>
+          <t>COP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>currency_choices</t>
+          <t>delivery_method_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_'cop'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 'COP'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'name':_'standard'}</t>
+          <t>expedited</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'name': 'Standard'}</t>
+          <t>Expedited</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'name':_'expedited'}</t>
+          <t>express</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'name': 'Expedited'}</t>
+          <t>Express</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'name':_'express'}</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'name': 'Express'}</t>
+          <t>Free</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'name':_'free'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'name': 'Free'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>delivery_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'name':_'pending'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'name': 'Pending'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'name':_'paid'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'name': 'Paid'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'name':_'cancelled'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'name': 'Cancelled'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'name':_'failed'}</t>
+          <t>refunded</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'name': 'Failed'}</t>
+          <t>Refunded</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>payment_gateway_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'name':_'refunded'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'name': 'Refunded'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'name':_'stripe'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'name': 'Stripe'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'name':_'paypal'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'name': 'PayPal'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'name':_'square'}</t>
+          <t>authorise</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'name': 'Square'}</t>
+          <t>Authorise</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'name':_'authorise'}</t>
+          <t>payoneer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'name': 'Authorise'}</t>
+          <t>Payoneer</t>
         </is>
       </c>
     </row>
@@ -1896,97 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'name':_'payoneer'}</t>
+          <t>paymaya</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'name': 'Payoneer'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'name':_'paymaya'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'name': 'Paymaya'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'name':_'authorise'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'name': 'Authorise'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'name':_'paymaya'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'name': 'Paymaya'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'name':_'stripe'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'name': 'Stripe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'name':_'square'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'name': 'Square'}</t>
+          <t>Paymaya</t>
         </is>
       </c>
     </row>
